--- a/docs/05_Bug-Report/Bug_Report.xlsx
+++ b/docs/05_Bug-Report/Bug_Report.xlsx
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
-  <si>
-    <t>항목</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>Bug ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,10 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BUG-001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -87,28 +79,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Window 10 / Chrome</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
-    <t>1~4단계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로그인 성공 후 메인 화면 이동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로그인되지 않음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Open</t>
   </si>
   <si>
+    <t>Open</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Severity</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -137,10 +117,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Open</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Assigned</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -162,6 +138,24 @@
   </si>
   <si>
     <t>Bug Report</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windows 10 / Chrome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 로그인 화면으로 이동한다.
+2. 올바른 아이디를 입력한다.
+3. 올바른 비밀번호를 입력한다.
+4. 로그인 버튼을 클릭한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인에 성공하고 메인 화면으로 이동한다.</t>
+  </si>
+  <si>
+    <t>로그인되지 않는다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -237,9 +231,7 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -247,12 +239,8 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -264,12 +252,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -557,116 +548,103 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.625" customWidth="1"/>
+    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="41.875" customWidth="1"/>
-    <col min="7" max="7" width="31.25" customWidth="1"/>
-    <col min="8" max="9" width="73.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.875" customWidth="1"/>
+    <col min="8" max="8" width="41.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
     <col min="11" max="12" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="3"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="26.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -678,19 +656,19 @@
           <x14:formula1>
             <xm:f>Code!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B8</xm:sqref>
+          <xm:sqref>F3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Code!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B7</xm:sqref>
+          <xm:sqref>E3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Code!$C$2:$C$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B12</xm:sqref>
+          <xm:sqref>J3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -708,71 +686,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/05_Bug-Report/Bug_Report.xlsx
+++ b/docs/05_Bug-Report/Bug_Report.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laypop-sykim\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070985ED-75DF-4E04-8E14-1D7DF3875EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29265" yWindow="240" windowWidth="36795" windowHeight="17850"/>
+    <workbookView xWindow="960" yWindow="780" windowWidth="27600" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
   <si>
     <t>Bug ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,10 +73,6 @@
   </si>
   <si>
     <t>Login</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>올바른 계정 정보 입력 후 로그인되지 않음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -158,11 +155,71 @@
     <t>로그인되지 않는다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>BUG-002</t>
+  </si>
+  <si>
+    <t>BUG-003</t>
+  </si>
+  <si>
+    <t>Signup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력한 비밀번호가 조건에 부합하지 않으나 회원가입 완료됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>비밀번호가 조건에 부합하지 않다는 에러 메시지가 발생한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원가입이 완료된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'manu'로 표시되어있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'menu'로 표시되어있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>올바른 계정 정보를 입력했으나 로그인되지 않음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 회원가입 화면으로 이동한다.
+2. 비밀번호를 제외한 필수 정보를 입력한다.
+3. 조건에 부합하지 않은 비밀번호를 입력한다.
+4. 가입하기 버튼을 클릭한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴 탭 오타 발생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 홈 페이지 메인 화면으로 이동한다.
+2. 메뉴 탭 중 'menu'탭 내용을 확인한다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -252,20 +309,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,36 +616,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="3" max="3" width="7.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.625" customWidth="1"/>
     <col min="5" max="5" width="15.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.875" customWidth="1"/>
-    <col min="8" max="8" width="41.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.5" customWidth="1"/>
+    <col min="8" max="8" width="53.375" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
     <col min="11" max="12" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
+      <c r="A1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -610,36 +679,100 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>14</v>
+    </row>
+    <row r="5" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -652,23 +785,23 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Code!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F3</xm:sqref>
+          <xm:sqref>F3:F5</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Code!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>E3</xm:sqref>
+          <xm:sqref>E3:E5</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>Code!$C$2:$C$7</xm:f>
           </x14:formula1>
-          <xm:sqref>J3</xm:sqref>
+          <xm:sqref>J3:J5</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -677,7 +810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -686,71 +819,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
